--- a/sample_data/erzeugt/Angebot_Kopfdaten_quer_verteilt.xlsx
+++ b/sample_data/erzeugt/Angebot_Kopfdaten_quer_verteilt.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
     </row>
